--- a/data/skill_usage_log.xlsx
+++ b/data/skill_usage_log.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,28 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:55:23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>阳阳</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>马静-调研问卷生成survey-generator+readme.zip</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>领取</t>
         </is>
@@ -647,11 +669,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-21 13:59:44</t>
+          <t>2026-04-21 15:55:23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/data/skill_usage_log.xlsx
+++ b/data/skill_usage_log.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,28 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:14:39</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>阳阳</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>邓风华的Skills和工作流程openclaw_full_Skills+readme.zip</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>领取</t>
         </is>
@@ -597,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +704,26 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>邓风华的Skills和工作流程openclaw_full_Skills+readme.zip</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:14:39</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>阳阳</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/skill_usage_log.xlsx
+++ b/data/skill_usage_log.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,28 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:14:55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>阳阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>邓风华的多角色协作协同(万能配置版)multi-role-system-template+readme.zip</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>领取</t>
         </is>
@@ -619,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +746,26 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>邓风华的多角色协作协同(万能配置版)multi-role-system-template+readme.zip</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:14:55</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>阳阳</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/skill_usage_log.xlsx
+++ b/data/skill_usage_log.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,28 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>领取</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:57:04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>罗琦企业调研技能</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>领取</t>
         </is>
